--- a/tests/data/empty_and_unnamed_rows.xlsx
+++ b/tests/data/empty_and_unnamed_rows.xlsx
@@ -419,17 +419,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Budget Bucket</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Estimation</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Epic Description</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Estimation</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Budget Bucket</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer Bruto Capacity</t>
+          <t>Engineer Capacity (Bruto)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -465,7 +465,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Manager Bruto Capacity</t>
+          <t>Management Capacity (Bruto)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer Absence (days)</t>
+          <t>Engineer Absence</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -493,7 +493,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -501,7 +501,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -527,15 +527,15 @@
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>Feature</t>
